--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91288</v>
+        <v>91293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92840</v>
+        <v>92848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128633169</v>
+        <v>128666421</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552087</v>
+        <v>552050</v>
       </c>
       <c r="R2" t="n">
-        <v>6842744</v>
+        <v>6842707</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Helt intill bäcken. Norra sidan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,58 +769,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128632620</v>
+        <v>128632785</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552066</v>
+        <v>552112</v>
       </c>
       <c r="R3" t="n">
-        <v>6842703</v>
+        <v>6842733</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5 fröställningar från i år</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,14 +890,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128632785</v>
+        <v>128668179</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -930,7 +920,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552112</v>
+        <v>552097</v>
       </c>
       <c r="R4" t="n">
-        <v>6842733</v>
+        <v>6842742</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,6 +974,11 @@
           <t>2025-09-22</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer på förmodad kolbotten. tillsammans med knärot.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -997,26 +992,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128668179</v>
+        <v>128670325</v>
       </c>
       <c r="B5" t="n">
-        <v>92826</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1039,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552097</v>
+        <v>552083</v>
       </c>
       <c r="R5" t="n">
-        <v>6842742</v>
+        <v>6842727</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på förmodad kolbotten. tillsammans med knärot.</t>
+          <t>Vid förmodad kojruin.Tillsammans med knärot.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128666699</v>
+        <v>128632620</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,12 +1148,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1170,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552076</v>
+        <v>552066</v>
       </c>
       <c r="R6" t="n">
-        <v>6842720</v>
+        <v>6842703</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1205,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ovanlig växtplats, helt intill bäcken, mycket fuktigt.</t>
+          <t>5 fröställningar från i år</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,57 +1221,58 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128670325</v>
+        <v>128633169</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552083</v>
+        <v>552087</v>
       </c>
       <c r="R7" t="n">
-        <v>6842727</v>
+        <v>6842744</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,11 +1318,6 @@
           <t>2025-09-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid förmodad kojruin.Tillsammans med knärot.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1340,22 +1331,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128668071</v>
+        <v>128666699</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,8 +1371,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1391,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552097</v>
+        <v>552076</v>
       </c>
       <c r="R8" t="n">
-        <v>6842742</v>
+        <v>6842720</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,7 +1430,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växtplatsen är en förmodad kolningsplats. Finns tyvärr inte inlagd på Fornsök. Knäroten växer tillsammans med och bland dropptaggsvamp.</t>
+          <t>Ovanlig växtplats, helt intill bäcken, mycket fuktigt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,36 +1458,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128668365</v>
+        <v>128668071</v>
       </c>
       <c r="B9" t="n">
-        <v>92855</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1496,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552105</v>
+        <v>552097</v>
       </c>
       <c r="R9" t="n">
-        <v>6842738</v>
+        <v>6842742</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,6 +1533,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växtplatsen är en förmodad kolningsplats. Finns tyvärr inte inlagd på Fornsök. Knäroten växer tillsammans med och bland dropptaggsvamp.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,37 +1565,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128666421</v>
+        <v>128669319</v>
       </c>
       <c r="B10" t="n">
-        <v>91305</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1597,13 +1612,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552050</v>
+        <v>552105</v>
       </c>
       <c r="R10" t="n">
-        <v>6842707</v>
+        <v>6842738</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,7 +1652,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Helt intill bäcken. Norra sidan.</t>
+          <t>Växer på förmodad kolbotten tillsammans med svart taggsvamp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,7 +1673,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1668,7 +1683,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128669319</v>
+        <v>128670766</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,7 +1825,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1827,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552105</v>
+        <v>552010</v>
       </c>
       <c r="R12" t="n">
-        <v>6842738</v>
+        <v>6842772</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,11 +1878,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer på förmodad kolbotten tillsammans med svart taggsvamp.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128666421</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128632785</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128668179</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128670325</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128632620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128633169</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128666699</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128668071</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669319</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128670372</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,8 +1957,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128670766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>